--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.132.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.132.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.132.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.132.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -595,7 +595,7 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): NoTE (odd internal casing) :: NoTE.â€” This form may be varied according to</t>
+          <t>L118: suspicious token(s): NoTE (odd internal casing) :: NoTE.— This form may be varied according to</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
@@ -605,16 +605,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L37: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: p Ã¦ ena see form under the 77th Compared with</t>
+          <t>L78: stray/suspicious non-ASCII glyph(s): U+2103 DEGREE CELSIUS :: f ℃.</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: testatorâ€™s personal assets. legacy.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]125</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]125</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L30: isolated marker/symbol line :: s.</t>
@@ -622,13 +626,13 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L27: isolated marker/symbol line :: 1</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]125</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L39: punctuation artifact: double/multiple hyphen :: a legatee to the amount of Â£-----------, under the will,</t>
+          <t>L39: punctuation artifact: double/multiple hyphen :: a legatee to the amount of £-----------, under the will,</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -670,16 +674,8 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the said legacy of Â£â€”â€”, together</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: dated the ---------day of --------â€”,of ----------,late</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -689,13 +685,13 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: &amp;c.</t>
+          <t>L27: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: dated the ---------day of --------â€”,of ----------,late</t>
+          <t>L41: punctuation artifact: double/multiple hyphen :: dated the ---------day of --------—,of ----------,late</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
@@ -729,16 +725,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (as in form 1) pray subpanaÃ¦na,</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tatorâ€™s death), is now due and owing to him the said A.</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -748,7 +736,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: /</t>
+          <t>L100: isolated marker/symbol line :: &amp;c.</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -774,12 +762,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -788,16 +776,8 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): NoTE (odd internal casing) :: NoTE.â€” This form may be varied according to</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NOTE.â€”This form may be varied according to the circumstances</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -805,7 +785,11 @@
           <t>L34: isolated marker/symbol line :: 2.</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L124: isolated marker/symbol line :: /</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr">
         <is>
@@ -843,16 +827,8 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L128: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: and the above in the form of a bill â€” a</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: arising from the latter being in the form of a Â« claimâ€�,</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -898,16 +874,8 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L137: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ng in the form of a"claimâ€�,â€�,</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: and the above in the form of a billâ€”a difference which</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -919,7 +887,7 @@
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L49: punctuation artifact: double/multiple hyphen :: the said legacy of Â£----------, together with interest</t>
+          <t>L49: punctuation artifact: double/multiple hyphen :: the said legacy of £----------, together with interest</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
@@ -953,11 +921,7 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L138: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of a bill â€” a difference which</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
@@ -1029,12 +993,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1073,7 +1037,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1112,7 +1076,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
